--- a/artfynd/A 19777-2020 artfynd.xlsx
+++ b/artfynd/A 19777-2020 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120160721</v>
+        <v>120167237</v>
       </c>
       <c r="B2" t="n">
         <v>57310</v>
@@ -716,14 +716,14 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Danielflon, Danielflon, Jmt</t>
+          <t>Lill-Abborrtjärnen, Lill-Abborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>474577</v>
+        <v>475135</v>
       </c>
       <c r="R2" t="n">
-        <v>7072319</v>
+        <v>7072298</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120167237</v>
+        <v>120160721</v>
       </c>
       <c r="B3" t="n">
         <v>57310</v>
@@ -823,14 +823,14 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lill-Abborrtjärnen, Lill-Abborrtjärnen, Jmt</t>
+          <t>Danielflon, Danielflon, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>475135</v>
+        <v>474577</v>
       </c>
       <c r="R3" t="n">
-        <v>7072298</v>
+        <v>7072319</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 19777-2020 artfynd.xlsx
+++ b/artfynd/A 19777-2020 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120167237</v>
+        <v>120160721</v>
       </c>
       <c r="B2" t="n">
         <v>57310</v>
@@ -716,14 +716,14 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lill-Abborrtjärnen, Lill-Abborrtjärnen, Jmt</t>
+          <t>Danielflon, Danielflon, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>475135</v>
+        <v>474577</v>
       </c>
       <c r="R2" t="n">
-        <v>7072298</v>
+        <v>7072319</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120160721</v>
+        <v>120167237</v>
       </c>
       <c r="B3" t="n">
         <v>57310</v>
@@ -823,14 +823,14 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Danielflon, Danielflon, Jmt</t>
+          <t>Lill-Abborrtjärnen, Lill-Abborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>474577</v>
+        <v>475135</v>
       </c>
       <c r="R3" t="n">
-        <v>7072319</v>
+        <v>7072298</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 19777-2020 artfynd.xlsx
+++ b/artfynd/A 19777-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>120160721</v>
       </c>
       <c r="B2" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>120167237</v>
       </c>
       <c r="B3" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 19777-2020 artfynd.xlsx
+++ b/artfynd/A 19777-2020 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120160721</v>
+        <v>120167237</v>
       </c>
       <c r="B2" t="n">
         <v>57320</v>
@@ -716,14 +716,14 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Danielflon, Danielflon, Jmt</t>
+          <t>Lill-Abborrtjärnen, Lill-Abborrtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>474577</v>
+        <v>475135</v>
       </c>
       <c r="R2" t="n">
-        <v>7072319</v>
+        <v>7072298</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120167237</v>
+        <v>120160721</v>
       </c>
       <c r="B3" t="n">
         <v>57320</v>
@@ -823,14 +823,14 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lill-Abborrtjärnen, Lill-Abborrtjärnen, Jmt</t>
+          <t>Danielflon, Danielflon, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>475135</v>
+        <v>474577</v>
       </c>
       <c r="R3" t="n">
-        <v>7072298</v>
+        <v>7072319</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
